--- a/A_2018/chrXIII:291925-340579_681_finemapping.xlsx
+++ b/A_2018/chrXIII:291925-340579_681_finemapping.xlsx
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">Biosynthesis of secondary metabolites - Saccharomyces cerevisiae (budding yeast)</t>
   </si>
   <si>
-    <t xml:space="preserve">62/270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300/1914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAL061W/YAR015W/YBL068W/YBR003W/YBR117C/YBR196C/YDL131W/YDL078C/YDL015C/YDR148C/YDR178W/YDR226W/YDR248C/YDR321W/YDR399W/YDR502C/YER081W/YER099C/YER141W/YER170W/YFL030W/YFL018C/YFR055W/YGL205W/YGR088W/YGR205W/YGR208W/YGR244C/YGR255C/YGR256W/YHL011C/YIL155C/YIL125W/YIL094C/YJL052W/YKL148C/YKL141W/YKL085W/YKR058W/YKR067W/YKR089C/YLL041C/YLR164W/YLR174W/YLR180W/YLR304C/YLR359W/YLR438W/YNL280C/YNL274C/YNL037C/YNR001C/YOL126C/YOR128C/YOR136W/YOR142W/YOR221C/YPL262W/YPL172C/YPL111W/YPR001W/YPR060C</t>
+    <t xml:space="preserve">63/270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308/1914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAL061W/YAR015W/YBL068W/YBR003W/YBR117C/YBR196C/YDL131W/YDL078C/YDL015C/YDR148C/YDR178W/YDR226W/YDR248C/YDR321W/YDR399W/YDR502C/YER081W/YER099C/YER141W/YER170W/YFL030W/YFL018C/YFR055W/YGL205W/YGR088W/YGR205W/YGR208W/YGR244C/YGR255C/YGR256W/YHL011C/YIL155C/YIL125W/YIL094C/YJL052W/YKL148C/YKL141W/YKL085W/YKR058W/YKR067W/YKR089C/YLL041C/YLR164W/YLR174W/YLR180W/YLR304C/YLR359W/YLR438W/YNL280C/YNL274C/YNL037C/YNR001C/YOL126C/YOR128C/YOR136W/YOR142W/YOR221C/YPL262W/YPL172C/YPL111W/YPR001W/YPR060C/YPR069C</t>
   </si>
   <si>
     <t xml:space="preserve">classic_adj</t>
@@ -77488,10 +77488,10 @@
         <v>0.0000000000000000462572308512085</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00000000000000393186462235272</v>
+        <v>0.00000000000000397812185320393</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00000000000000355450300225076</v>
+        <v>0.0000000000000036031948241994</v>
       </c>
       <c r="J2" t="s">
         <v>389</v>
@@ -77523,10 +77523,10 @@
         <v>0.0000000000156181079140683</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000000000663769586347902</v>
+        <v>0.000000000671578640304936</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000000000600064146172097</v>
+        <v>0.000000000608284202968975</v>
       </c>
       <c r="J3" t="s">
         <v>395</v>
@@ -77558,10 +77558,10 @@
         <v>0.00000000502727318242093</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00000014243940683526</v>
+        <v>0.000000144115164562733</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00000012876875169008</v>
+        <v>0.000000130532707192684</v>
       </c>
       <c r="J4" t="s">
         <v>400</v>
@@ -77593,10 +77593,10 @@
         <v>0.00000295646248712116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0000628248278513246</v>
+        <v>0.0000635639434731049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0000567952004104854</v>
+        <v>0.0000575732168544646</v>
       </c>
       <c r="J5" t="s">
         <v>407</v>
@@ -77628,10 +77628,10 @@
         <v>0.0000748810363730436</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00127297761834174</v>
+        <v>0.00128795382561635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00115080329583835</v>
+        <v>0.00116656772454847</v>
       </c>
       <c r="J6" t="s">
         <v>412</v>
@@ -77660,19 +77660,19 @@
         <v>416</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000433143399517704</v>
+        <v>0.000522261697560078</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00613619815983414</v>
+        <v>0.00748575099836112</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00554727511663024</v>
+        <v>0.00678023958235891</v>
       </c>
       <c r="J7" t="s">
         <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
